--- a/xlsx/Power/p7.xlsx
+++ b/xlsx/Power/p7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB9CB8A6-0894-4FF8-AC5A-F70954066ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D5DADE-F6D0-40FB-9137-B967E4F9E28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{DD0C3980-7A80-424A-BAC8-2E4733871900}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{DD0C3980-7A80-424A-BAC8-2E4733871900}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.32500000000000001</v>
       </c>
       <c r="C1">
-        <v>0.46500000000000002</v>
+        <v>9.2999999999999999E-2</v>
       </c>
       <c r="D1">
-        <v>0.61499999999999999</v>
+        <v>0.28100000000000003</v>
       </c>
       <c r="E1">
-        <v>0.66900000000000004</v>
+        <v>0.44</v>
       </c>
       <c r="F1">
-        <v>0.754</v>
+        <v>0.56699999999999995</v>
       </c>
       <c r="G1">
-        <v>0.81799999999999995</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="H1">
-        <v>0.89600000000000002</v>
+        <v>0.79600000000000004</v>
       </c>
       <c r="I1">
-        <v>0.93200000000000005</v>
+        <v>0.86599999999999999</v>
       </c>
       <c r="J1">
-        <v>0.93100000000000005</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.32200000000000001</v>
       </c>
       <c r="C2">
-        <v>0.45300000000000001</v>
+        <v>9.8000000000000004E-2</v>
       </c>
       <c r="D2">
-        <v>0.58499999999999996</v>
+        <v>0.28100000000000003</v>
       </c>
       <c r="E2">
-        <v>0.65200000000000002</v>
+        <v>0.435</v>
       </c>
       <c r="F2">
-        <v>0.73499999999999999</v>
+        <v>0.55700000000000005</v>
       </c>
       <c r="G2">
-        <v>0.80300000000000005</v>
+        <v>0.67100000000000004</v>
       </c>
       <c r="H2">
-        <v>0.88200000000000001</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="I2">
-        <v>0.91800000000000004</v>
+        <v>0.85699999999999998</v>
       </c>
       <c r="J2">
-        <v>0.91700000000000004</v>
+        <v>0.86499999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,39 +468,39 @@
         <v>0.29199999999999998</v>
       </c>
       <c r="C3">
-        <v>0.39800000000000002</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="D3">
-        <v>0.54200000000000004</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="E3">
-        <v>0.58699999999999997</v>
+        <v>0.59299999999999997</v>
       </c>
       <c r="F3">
-        <v>0.67400000000000004</v>
+        <v>0.68100000000000005</v>
       </c>
       <c r="G3">
         <v>0.73599999999999999</v>
       </c>
       <c r="H3">
-        <v>0.82499999999999996</v>
+        <v>0.82699999999999996</v>
       </c>
       <c r="I3">
-        <v>0.85499999999999998</v>
+        <v>0.85599999999999998</v>
       </c>
       <c r="J3">
-        <v>0.86899999999999999</v>
+        <v>0.874</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.13900000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="B4">
-        <v>0.247</v>
+        <v>0.26</v>
       </c>
       <c r="C4">
-        <v>0.36499999999999999</v>
+        <v>0.36899999999999999</v>
       </c>
       <c r="D4">
         <v>0.49399999999999999</v>
@@ -509,19 +509,19 @@
         <v>0.53700000000000003</v>
       </c>
       <c r="F4">
-        <v>0.61499999999999999</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="G4">
         <v>0.66400000000000003</v>
       </c>
       <c r="H4">
-        <v>0.77400000000000002</v>
+        <v>0.77300000000000002</v>
       </c>
       <c r="I4">
         <v>0.79600000000000004</v>
       </c>
       <c r="J4">
-        <v>0.82799999999999996</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,19 +532,19 @@
         <v>0.52900000000000003</v>
       </c>
       <c r="C5">
-        <v>0.88900000000000001</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="D5">
-        <v>0.98899999999999999</v>
+        <v>0.29399999999999998</v>
       </c>
       <c r="E5">
-        <v>0.997</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0.999</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -564,28 +564,28 @@
         <v>0.308</v>
       </c>
       <c r="C6">
-        <v>0.42899999999999999</v>
+        <v>0.58299999999999996</v>
       </c>
       <c r="D6">
-        <v>0.53900000000000003</v>
+        <v>0.59099999999999997</v>
       </c>
       <c r="E6">
-        <v>0.60199999999999998</v>
+        <v>0.64700000000000002</v>
       </c>
       <c r="F6">
-        <v>0.68799999999999994</v>
+        <v>0.71299999999999997</v>
       </c>
       <c r="G6">
-        <v>0.77400000000000002</v>
+        <v>0.78100000000000003</v>
       </c>
       <c r="H6">
-        <v>0.83499999999999996</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="I6">
-        <v>0.9</v>
+        <v>0.90800000000000003</v>
       </c>
       <c r="J6">
-        <v>0.89</v>
+        <v>0.89800000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>0.28899999999999998</v>
       </c>
       <c r="C7">
-        <v>0.41399999999999998</v>
+        <v>0.40899999999999997</v>
       </c>
       <c r="D7">
         <v>0.504</v>
       </c>
       <c r="E7">
-        <v>0.57199999999999995</v>
+        <v>0.57699999999999996</v>
       </c>
       <c r="F7">
-        <v>0.64200000000000002</v>
+        <v>0.63700000000000001</v>
       </c>
       <c r="G7">
-        <v>0.73299999999999998</v>
+        <v>0.72699999999999998</v>
       </c>
       <c r="H7">
         <v>0.79800000000000004</v>
       </c>
       <c r="I7">
-        <v>0.86399999999999999</v>
+        <v>0.86199999999999999</v>
       </c>
       <c r="J7">
-        <v>0.86799999999999999</v>
+        <v>0.86699999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.19</v>
       </c>
       <c r="C8">
-        <v>0.26700000000000002</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0.35399999999999998</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="E8">
-        <v>0.39</v>
+        <v>0.14899999999999999</v>
       </c>
       <c r="F8">
-        <v>0.46200000000000002</v>
+        <v>0.25900000000000001</v>
       </c>
       <c r="G8">
-        <v>0.50900000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="H8">
-        <v>0.58299999999999996</v>
+        <v>0.41</v>
       </c>
       <c r="I8">
-        <v>0.70399999999999996</v>
+        <v>0.23499999999999999</v>
       </c>
       <c r="J8">
-        <v>0.69399999999999995</v>
+        <v>0.26900000000000002</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>0.16500000000000001</v>
       </c>
       <c r="C9">
-        <v>0.13200000000000001</v>
+        <v>0.44800000000000001</v>
       </c>
       <c r="D9">
-        <v>0.16700000000000001</v>
+        <v>0.89500000000000002</v>
       </c>
       <c r="E9">
-        <v>0.215</v>
+        <v>0.68500000000000005</v>
       </c>
       <c r="F9">
-        <v>0.21299999999999999</v>
+        <v>0.38500000000000001</v>
       </c>
       <c r="G9">
-        <v>0.28100000000000003</v>
+        <v>0.376</v>
       </c>
       <c r="H9">
-        <v>0.32800000000000001</v>
+        <v>0.375</v>
       </c>
       <c r="I9">
-        <v>0.377</v>
+        <v>0.40699999999999997</v>
       </c>
       <c r="J9">
-        <v>0.41499999999999998</v>
+        <v>0.435</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p7.xlsx
+++ b/xlsx/Power/p7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D5DADE-F6D0-40FB-9137-B967E4F9E28D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375C3E6F-4DDB-489B-B4CD-0005AEF9F368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{DD0C3980-7A80-424A-BAC8-2E4733871900}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{DD0C3980-7A80-424A-BAC8-2E4733871900}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.32500000000000001</v>
       </c>
       <c r="C1">
-        <v>9.2999999999999999E-2</v>
+        <v>0.46500000000000002</v>
       </c>
       <c r="D1">
-        <v>0.28100000000000003</v>
+        <v>0.61499999999999999</v>
       </c>
       <c r="E1">
-        <v>0.44</v>
+        <v>0.66900000000000004</v>
       </c>
       <c r="F1">
-        <v>0.56699999999999995</v>
+        <v>0.754</v>
       </c>
       <c r="G1">
-        <v>0.67500000000000004</v>
+        <v>0.81799999999999995</v>
       </c>
       <c r="H1">
-        <v>0.79600000000000004</v>
+        <v>0.89600000000000002</v>
       </c>
       <c r="I1">
-        <v>0.86599999999999999</v>
+        <v>0.93200000000000005</v>
       </c>
       <c r="J1">
-        <v>0.877</v>
+        <v>0.93100000000000005</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.32200000000000001</v>
       </c>
       <c r="C2">
-        <v>9.8000000000000004E-2</v>
+        <v>0.45300000000000001</v>
       </c>
       <c r="D2">
-        <v>0.28100000000000003</v>
+        <v>0.58499999999999996</v>
       </c>
       <c r="E2">
-        <v>0.435</v>
+        <v>0.65200000000000002</v>
       </c>
       <c r="F2">
-        <v>0.55700000000000005</v>
+        <v>0.73499999999999999</v>
       </c>
       <c r="G2">
-        <v>0.67100000000000004</v>
+        <v>0.80300000000000005</v>
       </c>
       <c r="H2">
-        <v>0.77500000000000002</v>
+        <v>0.88200000000000001</v>
       </c>
       <c r="I2">
-        <v>0.85699999999999998</v>
+        <v>0.91800000000000004</v>
       </c>
       <c r="J2">
-        <v>0.86499999999999999</v>
+        <v>0.91700000000000004</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,39 +468,39 @@
         <v>0.29199999999999998</v>
       </c>
       <c r="C3">
-        <v>0.44900000000000001</v>
+        <v>0.39800000000000002</v>
       </c>
       <c r="D3">
-        <v>0.54500000000000004</v>
+        <v>0.54200000000000004</v>
       </c>
       <c r="E3">
-        <v>0.59299999999999997</v>
+        <v>0.58699999999999997</v>
       </c>
       <c r="F3">
-        <v>0.68100000000000005</v>
+        <v>0.67400000000000004</v>
       </c>
       <c r="G3">
         <v>0.73599999999999999</v>
       </c>
       <c r="H3">
-        <v>0.82699999999999996</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="I3">
-        <v>0.85599999999999998</v>
+        <v>0.85499999999999998</v>
       </c>
       <c r="J3">
-        <v>0.874</v>
+        <v>0.86899999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.156</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="B4">
-        <v>0.26</v>
+        <v>0.247</v>
       </c>
       <c r="C4">
-        <v>0.36899999999999999</v>
+        <v>0.36499999999999999</v>
       </c>
       <c r="D4">
         <v>0.49399999999999999</v>
@@ -509,19 +509,19 @@
         <v>0.53700000000000003</v>
       </c>
       <c r="F4">
-        <v>0.61699999999999999</v>
+        <v>0.61499999999999999</v>
       </c>
       <c r="G4">
         <v>0.66400000000000003</v>
       </c>
       <c r="H4">
-        <v>0.77300000000000002</v>
+        <v>0.77400000000000002</v>
       </c>
       <c r="I4">
         <v>0.79600000000000004</v>
       </c>
       <c r="J4">
-        <v>0.83</v>
+        <v>0.82799999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,19 +532,19 @@
         <v>0.52900000000000003</v>
       </c>
       <c r="C5">
-        <v>5.0000000000000001E-3</v>
+        <v>0.88900000000000001</v>
       </c>
       <c r="D5">
-        <v>0.29399999999999998</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="E5">
-        <v>0.84099999999999997</v>
+        <v>0.997</v>
       </c>
       <c r="F5">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>0.999</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -564,60 +564,60 @@
         <v>0.308</v>
       </c>
       <c r="C6">
-        <v>0.58299999999999996</v>
+        <v>0.42899999999999999</v>
       </c>
       <c r="D6">
-        <v>0.59099999999999997</v>
+        <v>0.53900000000000003</v>
       </c>
       <c r="E6">
-        <v>0.64700000000000002</v>
+        <v>0.60199999999999998</v>
       </c>
       <c r="F6">
-        <v>0.71299999999999997</v>
+        <v>0.68799999999999994</v>
       </c>
       <c r="G6">
-        <v>0.78100000000000003</v>
+        <v>0.77400000000000002</v>
       </c>
       <c r="H6">
-        <v>0.84499999999999997</v>
+        <v>0.83499999999999996</v>
       </c>
       <c r="I6">
-        <v>0.90800000000000003</v>
+        <v>0.9</v>
       </c>
       <c r="J6">
-        <v>0.89800000000000002</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.13800000000000001</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="B7">
         <v>0.28899999999999998</v>
       </c>
       <c r="C7">
-        <v>0.40899999999999997</v>
+        <v>0.41399999999999998</v>
       </c>
       <c r="D7">
         <v>0.504</v>
       </c>
       <c r="E7">
-        <v>0.57699999999999996</v>
+        <v>0.57199999999999995</v>
       </c>
       <c r="F7">
-        <v>0.63700000000000001</v>
+        <v>0.64200000000000002</v>
       </c>
       <c r="G7">
-        <v>0.72699999999999998</v>
+        <v>0.73299999999999998</v>
       </c>
       <c r="H7">
         <v>0.79800000000000004</v>
       </c>
       <c r="I7">
-        <v>0.86199999999999999</v>
+        <v>0.86399999999999999</v>
       </c>
       <c r="J7">
-        <v>0.86699999999999999</v>
+        <v>0.86799999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.19</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="D8">
-        <v>6.8000000000000005E-2</v>
+        <v>0.35399999999999998</v>
       </c>
       <c r="E8">
-        <v>0.14899999999999999</v>
+        <v>0.39</v>
       </c>
       <c r="F8">
-        <v>0.25900000000000001</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="G8">
-        <v>0.33</v>
+        <v>0.50900000000000001</v>
       </c>
       <c r="H8">
-        <v>0.41</v>
+        <v>0.58299999999999996</v>
       </c>
       <c r="I8">
-        <v>0.23499999999999999</v>
+        <v>0.70399999999999996</v>
       </c>
       <c r="J8">
-        <v>0.26900000000000002</v>
+        <v>0.69399999999999995</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>0.16500000000000001</v>
       </c>
       <c r="C9">
-        <v>0.44800000000000001</v>
+        <v>0.13200000000000001</v>
       </c>
       <c r="D9">
-        <v>0.89500000000000002</v>
+        <v>0.16700000000000001</v>
       </c>
       <c r="E9">
-        <v>0.68500000000000005</v>
+        <v>0.215</v>
       </c>
       <c r="F9">
-        <v>0.38500000000000001</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="G9">
-        <v>0.376</v>
+        <v>0.28100000000000003</v>
       </c>
       <c r="H9">
-        <v>0.375</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="I9">
-        <v>0.40699999999999997</v>
+        <v>0.377</v>
       </c>
       <c r="J9">
-        <v>0.435</v>
+        <v>0.41499999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p7.xlsx
+++ b/xlsx/Power/p7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{375C3E6F-4DDB-489B-B4CD-0005AEF9F368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FBF2233-2608-4032-A887-CD94B8C8AED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{DD0C3980-7A80-424A-BAC8-2E4733871900}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{DD0C3980-7A80-424A-BAC8-2E4733871900}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,19 +398,19 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.16300000000000001</v>
+        <v>0.161</v>
       </c>
       <c r="B1">
-        <v>0.32500000000000001</v>
+        <v>0.32700000000000001</v>
       </c>
       <c r="C1">
         <v>0.46500000000000002</v>
       </c>
       <c r="D1">
-        <v>0.61499999999999999</v>
+        <v>0.61599999999999999</v>
       </c>
       <c r="E1">
-        <v>0.66900000000000004</v>
+        <v>0.67</v>
       </c>
       <c r="F1">
         <v>0.754</v>
@@ -422,18 +422,18 @@
         <v>0.89600000000000002</v>
       </c>
       <c r="I1">
-        <v>0.93200000000000005</v>
+        <v>0.93400000000000005</v>
       </c>
       <c r="J1">
-        <v>0.93100000000000005</v>
+        <v>0.93400000000000005</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.155</v>
+        <v>0.152</v>
       </c>
       <c r="B2">
-        <v>0.32200000000000001</v>
+        <v>0.32600000000000001</v>
       </c>
       <c r="C2">
         <v>0.45300000000000001</v>
@@ -442,161 +442,161 @@
         <v>0.58499999999999996</v>
       </c>
       <c r="E2">
-        <v>0.65200000000000002</v>
+        <v>0.65100000000000002</v>
       </c>
       <c r="F2">
-        <v>0.73499999999999999</v>
+        <v>0.73399999999999999</v>
       </c>
       <c r="G2">
-        <v>0.80300000000000005</v>
+        <v>0.79900000000000004</v>
       </c>
       <c r="H2">
-        <v>0.88200000000000001</v>
+        <v>0.878</v>
       </c>
       <c r="I2">
-        <v>0.91800000000000004</v>
+        <v>0.92100000000000004</v>
       </c>
       <c r="J2">
-        <v>0.91700000000000004</v>
+        <v>0.91900000000000004</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.14599999999999999</v>
+        <v>0.14499999999999999</v>
       </c>
       <c r="B3">
-        <v>0.29199999999999998</v>
+        <v>0.29299999999999998</v>
       </c>
       <c r="C3">
-        <v>0.39800000000000002</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="D3">
-        <v>0.54200000000000004</v>
+        <v>0.54400000000000004</v>
       </c>
       <c r="E3">
-        <v>0.58699999999999997</v>
+        <v>0.59199999999999997</v>
       </c>
       <c r="F3">
         <v>0.67400000000000004</v>
       </c>
       <c r="G3">
-        <v>0.73599999999999999</v>
+        <v>0.73799999999999999</v>
       </c>
       <c r="H3">
-        <v>0.82499999999999996</v>
+        <v>0.83</v>
       </c>
       <c r="I3">
-        <v>0.85499999999999998</v>
+        <v>0.85899999999999999</v>
       </c>
       <c r="J3">
-        <v>0.86899999999999999</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.13900000000000001</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="B4">
-        <v>0.247</v>
+        <v>0.249</v>
       </c>
       <c r="C4">
-        <v>0.36499999999999999</v>
+        <v>0.36599999999999999</v>
       </c>
       <c r="D4">
         <v>0.49399999999999999</v>
       </c>
       <c r="E4">
-        <v>0.53700000000000003</v>
+        <v>0.53900000000000003</v>
       </c>
       <c r="F4">
-        <v>0.61499999999999999</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="G4">
-        <v>0.66400000000000003</v>
+        <v>0.67</v>
       </c>
       <c r="H4">
         <v>0.77400000000000002</v>
       </c>
       <c r="I4">
-        <v>0.79600000000000004</v>
+        <v>0.80200000000000005</v>
       </c>
       <c r="J4">
-        <v>0.82799999999999996</v>
+        <v>0.83099999999999996</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0.13900000000000001</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>0.52900000000000003</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="C5">
-        <v>0.88900000000000001</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D5">
-        <v>0.98899999999999999</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="E5">
-        <v>0.997</v>
+        <v>3.1E-2</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>5.0999999999999997E-2</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.14099999999999999</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="B6">
-        <v>0.308</v>
+        <v>0.307</v>
       </c>
       <c r="C6">
-        <v>0.42899999999999999</v>
+        <v>0.42699999999999999</v>
       </c>
       <c r="D6">
-        <v>0.53900000000000003</v>
+        <v>0.53500000000000003</v>
       </c>
       <c r="E6">
-        <v>0.60199999999999998</v>
+        <v>0.59799999999999998</v>
       </c>
       <c r="F6">
         <v>0.68799999999999994</v>
       </c>
       <c r="G6">
-        <v>0.77400000000000002</v>
+        <v>0.76400000000000001</v>
       </c>
       <c r="H6">
-        <v>0.83499999999999996</v>
+        <v>0.82699999999999996</v>
       </c>
       <c r="I6">
-        <v>0.9</v>
+        <v>0.89700000000000002</v>
       </c>
       <c r="J6">
-        <v>0.89</v>
+        <v>0.89200000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.13900000000000001</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="B7">
-        <v>0.28899999999999998</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="C7">
-        <v>0.41399999999999998</v>
+        <v>0.41199999999999998</v>
       </c>
       <c r="D7">
         <v>0.504</v>
@@ -605,10 +605,10 @@
         <v>0.57199999999999995</v>
       </c>
       <c r="F7">
-        <v>0.64200000000000002</v>
+        <v>0.63700000000000001</v>
       </c>
       <c r="G7">
-        <v>0.73299999999999998</v>
+        <v>0.73099999999999998</v>
       </c>
       <c r="H7">
         <v>0.79800000000000004</v>
@@ -625,28 +625,28 @@
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="B8">
-        <v>0.19</v>
+        <v>0.191</v>
       </c>
       <c r="C8">
         <v>0.26700000000000002</v>
       </c>
       <c r="D8">
-        <v>0.35399999999999998</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="E8">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="F8">
-        <v>0.46200000000000002</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="G8">
-        <v>0.50900000000000001</v>
+        <v>0.50800000000000001</v>
       </c>
       <c r="H8">
-        <v>0.58299999999999996</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="I8">
-        <v>0.70399999999999996</v>
+        <v>0.70499999999999996</v>
       </c>
       <c r="J8">
         <v>0.69399999999999995</v>
@@ -657,31 +657,31 @@
         <v>0.10100000000000001</v>
       </c>
       <c r="B9">
-        <v>0.16500000000000001</v>
+        <v>0.16900000000000001</v>
       </c>
       <c r="C9">
-        <v>0.13200000000000001</v>
+        <v>0.13400000000000001</v>
       </c>
       <c r="D9">
-        <v>0.16700000000000001</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="E9">
-        <v>0.215</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="F9">
-        <v>0.21299999999999999</v>
+        <v>0.214</v>
       </c>
       <c r="G9">
-        <v>0.28100000000000003</v>
+        <v>0.27800000000000002</v>
       </c>
       <c r="H9">
-        <v>0.32800000000000001</v>
+        <v>0.33100000000000002</v>
       </c>
       <c r="I9">
-        <v>0.377</v>
+        <v>0.378</v>
       </c>
       <c r="J9">
-        <v>0.41499999999999998</v>
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
